--- a/datagolf/workbooks/StatCaddy_Field_latest.xlsx
+++ b/datagolf/workbooks/StatCaddy_Field_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,32 +480,32 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.636</v>
+        <v>0.7286</v>
       </c>
       <c r="C2" t="n">
-        <v>0.185</v>
+        <v>1.4114</v>
       </c>
       <c r="D2" t="n">
-        <v>0.786</v>
+        <v>0.6914</v>
       </c>
       <c r="E2" t="n">
-        <v>0.218</v>
+        <v>-0.0086</v>
       </c>
       <c r="F2" t="n">
-        <v>0.125</v>
+        <v>0.1743</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="H2" t="n">
-        <v>1.77</v>
+        <v>1.18</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -521,32 +521,32 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.174</v>
+        <v>-0.4357</v>
       </c>
       <c r="C3" t="n">
-        <v>0.185</v>
+        <v>0.3371</v>
       </c>
       <c r="D3" t="n">
-        <v>0.393</v>
+        <v>0.1071</v>
       </c>
       <c r="E3" t="n">
-        <v>0.498</v>
+        <v>0.1343</v>
       </c>
       <c r="F3" t="n">
-        <v>0.16</v>
+        <v>0.2729</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="H3" t="n">
-        <v>0.88</v>
+        <v>0.23</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -562,32 +562,32 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7467</v>
+        <v>0.738</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4656</v>
+        <v>0.436</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3222</v>
+        <v>0.197</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0278</v>
+        <v>0.067</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.32</v>
+        <v>-0.344</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.21</v>
+        <v>-0.15</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8583</v>
+        <v>0.6771</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -603,32 +603,32 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.097</v>
+        <v>0.2025</v>
       </c>
       <c r="C5" t="n">
-        <v>0.185</v>
+        <v>0.4325</v>
       </c>
       <c r="D5" t="n">
-        <v>0.265</v>
+        <v>0.1837</v>
       </c>
       <c r="E5" t="n">
-        <v>0.401</v>
+        <v>0.3375</v>
       </c>
       <c r="F5" t="n">
-        <v>0.083</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="H5" t="n">
-        <v>0.85</v>
+        <v>1.02</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -644,32 +644,32 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.403</v>
+        <v>0.385</v>
       </c>
       <c r="C6" t="n">
-        <v>0.185</v>
+        <v>3.84</v>
       </c>
       <c r="D6" t="n">
-        <v>0.636</v>
+        <v>1.1383</v>
       </c>
       <c r="E6" t="n">
-        <v>0.607</v>
+        <v>0.8783</v>
       </c>
       <c r="F6" t="n">
-        <v>0.065</v>
+        <v>0.2917</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="H6" t="n">
-        <v>1.71</v>
+        <v>2.2267</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -685,32 +685,32 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.344</v>
+        <v>0.2729</v>
       </c>
       <c r="C7" t="n">
-        <v>0.185</v>
+        <v>0.9071</v>
       </c>
       <c r="D7" t="n">
-        <v>0.745</v>
+        <v>0.7533</v>
       </c>
       <c r="E7" t="n">
-        <v>0.194</v>
+        <v>0.26</v>
       </c>
       <c r="F7" t="n">
-        <v>0.21</v>
+        <v>0.0914</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.49</v>
+        <v>1.1175</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -722,36 +722,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ricky Castillo</t>
+          <t>Bud Cauley</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1214</v>
+        <v>0.38</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1743</v>
+        <v>0.6813</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0414</v>
+        <v>0.1825</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0386</v>
+        <v>0.0887</v>
       </c>
       <c r="F8" t="n">
-        <v>0.26</v>
+        <v>0.4062</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4367</v>
+        <v>0.994</v>
       </c>
       <c r="I8" t="n">
         <v>0.01</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -763,36 +763,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bud Cauley</t>
+          <t>Wyndham Clark</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3825</v>
+        <v>0.0688</v>
       </c>
       <c r="C9" t="n">
-        <v>0.55</v>
+        <v>2.9775</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3175</v>
+        <v>0.3187</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2037</v>
+        <v>0.8187</v>
       </c>
       <c r="F9" t="n">
-        <v>0.37</v>
+        <v>0.4125</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="H9" t="n">
-        <v>1.146</v>
+        <v>1.558</v>
       </c>
       <c r="I9" t="n">
-        <v>0.17</v>
+        <v>0.04</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -804,36 +804,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wyndham Clark</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.021</v>
+        <v>-0.308</v>
       </c>
       <c r="C10" t="n">
-        <v>0.185</v>
+        <v>0.479</v>
       </c>
       <c r="D10" t="n">
-        <v>0.272</v>
+        <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>0.508</v>
+        <v>0.632</v>
       </c>
       <c r="F10" t="n">
-        <v>0.352</v>
+        <v>0.358</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="H10" t="n">
-        <v>1.15</v>
+        <v>-0.0683</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -845,36 +845,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Nico Echavarria</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2589</v>
+        <v>0.0089</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5322</v>
+        <v>0.4244</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1322</v>
+        <v>0.1656</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7367</v>
+        <v>0.2456</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3044</v>
+        <v>0.0644</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.11</v>
+        <v>0.02</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3217</v>
+        <v>0.602</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -886,36 +886,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Corey Conners</t>
+          <t>Alex Fitzpatrick</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.318</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>0.185</v>
+        <v>0.8875</v>
       </c>
       <c r="D12" t="n">
-        <v>0.535</v>
+        <v>0.8538</v>
       </c>
       <c r="E12" t="n">
-        <v>0.005</v>
+        <v>-0.315</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.026</v>
+        <v>-0.0112</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="H12" t="n">
-        <v>0.83</v>
+        <v>0.28</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -927,36 +927,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pierceson Coody</t>
+          <t>Matt Fitzpatrick</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2145</v>
+        <v>0.06</v>
       </c>
       <c r="C13" t="n">
-        <v>0.26</v>
+        <v>2.0457</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6318</v>
+        <v>0.8629</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1418</v>
+        <v>0.24</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1927</v>
+        <v>0.57</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.4</v>
+        <v>2.2075</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.03</v>
+        <v>0.11</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -968,36 +968,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nico Echavarria</t>
+          <t>Tommy Fleetwood</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.0256</v>
+        <v>0.58</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2889</v>
+        <v>2.2043</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1833</v>
+        <v>0.5114</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2111</v>
+        <v>0.4143</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01</v>
+        <v>0.59</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1</v>
+        <v>-0.01</v>
       </c>
       <c r="H14" t="n">
-        <v>0.404</v>
+        <v>2.0425</v>
       </c>
       <c r="I14" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1009,36 +1009,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Harris English</t>
+          <t>Rickie Fowler</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3275</v>
+        <v>0.2838</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2087</v>
+        <v>0.5225</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2762</v>
+        <v>0.1588</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2025</v>
+        <v>0.13</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4575</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="H15" t="n">
-        <v>0.038</v>
+        <v>0.9925</v>
       </c>
       <c r="I15" t="n">
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1050,36 +1050,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alex Fitzpatrick</t>
+          <t>Ryan Fox</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.58</v>
+        <v>0.4057</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0762</v>
+        <v>0.6586</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0263</v>
+        <v>0.3186</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.25</v>
+        <v>0.2814</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0112</v>
+        <v>-0.1457</v>
       </c>
       <c r="G16" t="n">
-        <v>0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="H16" t="n">
-        <v>0.984</v>
+        <v>0.8325</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1091,36 +1091,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Matt Fitzpatrick</t>
+          <t>Ryan Gerard</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.293</v>
+        <v>0.3233</v>
       </c>
       <c r="C17" t="n">
-        <v>0.185</v>
+        <v>0.8089</v>
       </c>
       <c r="D17" t="n">
-        <v>0.826</v>
+        <v>0.1589</v>
       </c>
       <c r="E17" t="n">
-        <v>0.267</v>
+        <v>0.4111</v>
       </c>
       <c r="F17" t="n">
-        <v>0.406</v>
+        <v>0.1111</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="H17" t="n">
-        <v>1.79</v>
+        <v>0.916</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1132,36 +1132,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tommy Fleetwood</t>
+          <t>Chris Gotterup</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.509</v>
+        <v>0.7488</v>
       </c>
       <c r="C18" t="n">
-        <v>0.185</v>
+        <v>1.1075</v>
       </c>
       <c r="D18" t="n">
-        <v>0.627</v>
+        <v>0.5475</v>
       </c>
       <c r="E18" t="n">
-        <v>0.395</v>
+        <v>0.4113</v>
       </c>
       <c r="F18" t="n">
-        <v>0.329</v>
+        <v>-0.1913</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="H18" t="n">
-        <v>1.86</v>
+        <v>1.202</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1173,36 +1173,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rickie Fowler</t>
+          <t>Ben Griffin</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.331</v>
+        <v>0.0956</v>
       </c>
       <c r="C19" t="n">
-        <v>0.185</v>
+        <v>0.6933</v>
       </c>
       <c r="D19" t="n">
-        <v>0.297</v>
+        <v>0.4067</v>
       </c>
       <c r="E19" t="n">
-        <v>0.229</v>
+        <v>0.2433</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02</v>
+        <v>0.4522</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.88</v>
+        <v>0.712</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1214,36 +1214,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ryan Fox</t>
+          <t>Russell Henley</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.163</v>
+        <v>0.5017</v>
       </c>
       <c r="C20" t="n">
-        <v>0.185</v>
+        <v>1.0317</v>
       </c>
       <c r="D20" t="n">
-        <v>0.298</v>
+        <v>0.3</v>
       </c>
       <c r="E20" t="n">
-        <v>0.208</v>
+        <v>0.6983</v>
       </c>
       <c r="F20" t="n">
-        <v>0.022</v>
+        <v>-0.2133</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.3167</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1255,36 +1255,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ryan Gerard</t>
+          <t>Ryo Hisatsune</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.34</v>
+        <v>0.402</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7822</v>
+        <v>0.208</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2589</v>
+        <v>0.278</v>
       </c>
       <c r="E21" t="n">
-        <v>0.45</v>
+        <v>-0.363</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0144</v>
+        <v>-0.019</v>
       </c>
       <c r="G21" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="H21" t="n">
-        <v>1.238</v>
+        <v>0.298</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1296,36 +1296,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Chris Gotterup</t>
+          <t>Nicolai Hojgaard</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.729</v>
+        <v>0.1338</v>
       </c>
       <c r="C22" t="n">
-        <v>0.185</v>
+        <v>0.2975</v>
       </c>
       <c r="D22" t="n">
-        <v>0.543</v>
+        <v>0.2313</v>
       </c>
       <c r="E22" t="n">
-        <v>0.281</v>
+        <v>-0.0862</v>
       </c>
       <c r="F22" t="n">
-        <v>0.013</v>
+        <v>0.1425</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="H22" t="n">
-        <v>1.57</v>
+        <v>-0.184</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1337,36 +1337,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ben Griffin</t>
+          <t>Viktor Hovland</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1511</v>
+        <v>0.025</v>
       </c>
       <c r="C23" t="n">
-        <v>1.0378</v>
+        <v>1.11</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3156</v>
+        <v>0.9233</v>
       </c>
       <c r="E23" t="n">
-        <v>0.48</v>
+        <v>-0.0833</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5478</v>
+        <v>0.308</v>
       </c>
       <c r="G23" t="n">
         <v>-0.03</v>
       </c>
       <c r="H23" t="n">
-        <v>0.712</v>
+        <v>1.4125</v>
       </c>
       <c r="I23" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1378,36 +1378,36 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Harry Hall</t>
+          <t>Sungjae Im</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.512</v>
+        <v>0.3375</v>
       </c>
       <c r="C24" t="n">
-        <v>0.306</v>
+        <v>0.765</v>
       </c>
       <c r="D24" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.7729</v>
+      </c>
+      <c r="I24" t="n">
         <v>0.1</v>
       </c>
-      <c r="E24" t="n">
-        <v>-0.032</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-0.1567</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1419,36 +1419,36 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Brian Harman</t>
+          <t>Si Woo Kim</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1178</v>
+        <v>0.4213</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3222</v>
+        <v>1.7263</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2633</v>
+        <v>0.7825</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4311</v>
+        <v>0.0612</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0589</v>
+        <v>0.2275</v>
       </c>
       <c r="G25" t="n">
-        <v>0.18</v>
+        <v>0.02</v>
       </c>
       <c r="H25" t="n">
-        <v>0.586</v>
+        <v>1.4075</v>
       </c>
       <c r="I25" t="n">
-        <v>0.13</v>
+        <v>0.02</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1460,36 +1460,36 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Russell Henley</t>
+          <t>Tom Kim</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.258</v>
+        <v>0.0267</v>
       </c>
       <c r="C26" t="n">
-        <v>0.185</v>
+        <v>1.8578</v>
       </c>
       <c r="D26" t="n">
-        <v>0.435</v>
+        <v>1.1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.404</v>
+        <v>0.1633</v>
       </c>
       <c r="F26" t="n">
-        <v>0.114</v>
+        <v>0.1733</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.21</v>
+        <v>1.7083</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1501,36 +1501,36 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ryo Hisatsune</t>
+          <t>Kurt Kitayama</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.344</v>
+        <v>0.4214</v>
       </c>
       <c r="C27" t="n">
-        <v>0.208</v>
+        <v>0.6543</v>
       </c>
       <c r="D27" t="n">
-        <v>0.214</v>
+        <v>0.6486</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.279</v>
+        <v>0.1657</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.007</v>
+        <v>0.1286</v>
       </c>
       <c r="G27" t="n">
-        <v>0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="H27" t="n">
-        <v>0.16</v>
+        <v>0.9675</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1542,36 +1542,36 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nicolai Hojgaard</t>
+          <t>Jake Knapp</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.345</v>
+        <v>0.27</v>
       </c>
       <c r="C28" t="n">
-        <v>0.185</v>
+        <v>0.18</v>
       </c>
       <c r="D28" t="n">
-        <v>0.39</v>
+        <v>0.362</v>
       </c>
       <c r="E28" t="n">
-        <v>0.083</v>
+        <v>-0.104</v>
       </c>
       <c r="F28" t="n">
-        <v>0.063</v>
+        <v>-0.302</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="H28" t="n">
-        <v>0.88</v>
+        <v>0.028</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1583,36 +1583,36 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>Min Woo Lee</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.068</v>
+        <v>0.4617</v>
       </c>
       <c r="C29" t="n">
-        <v>0.185</v>
+        <v>0.425</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.003</v>
+        <v>0.2533</v>
       </c>
       <c r="E29" t="n">
-        <v>0.274</v>
+        <v>-0.41</v>
       </c>
       <c r="F29" t="n">
-        <v>0.024</v>
+        <v>0.1883</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="H29" t="n">
-        <v>0.36</v>
+        <v>-0.41</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1624,36 +1624,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Viktor Hovland</t>
+          <t>Robert MacIntyre</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.392</v>
+        <v>0.3925</v>
       </c>
       <c r="C30" t="n">
-        <v>0.185</v>
+        <v>0.5613</v>
       </c>
       <c r="D30" t="n">
-        <v>0.787</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>0.167</v>
+        <v>0.1663</v>
       </c>
       <c r="F30" t="n">
-        <v>0.157</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="H30" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1665,36 +1665,36 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sungjae Im</t>
+          <t>Hideki Matsuyama</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.3483</v>
+        <v>0.2</v>
       </c>
       <c r="C31" t="n">
-        <v>0.525</v>
+        <v>1.3144</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5058</v>
+        <v>0.4622</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2733</v>
+        <v>0.1067</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3133</v>
+        <v>0.3711</v>
       </c>
       <c r="G31" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="H31" t="n">
-        <v>0.7029</v>
+        <v>1.962</v>
       </c>
       <c r="I31" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -1706,36 +1706,36 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Michael Kim</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1364</v>
+        <v>-0.44</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3673</v>
+        <v>0.0944</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3045</v>
+        <v>-0.2389</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3118</v>
+        <v>0.6822</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0473</v>
+        <v>-0.3411</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2786</v>
+        <v>-0.12</v>
       </c>
       <c r="I32" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1747,36 +1747,36 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Si Woo Kim</t>
+          <t>Rory McIlroy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.423</v>
+        <v>1.17</v>
       </c>
       <c r="C33" t="n">
-        <v>0.185</v>
+        <v>1.116</v>
       </c>
       <c r="D33" t="n">
-        <v>0.744</v>
+        <v>0.108</v>
       </c>
       <c r="E33" t="n">
-        <v>0.12</v>
+        <v>0.44</v>
       </c>
       <c r="F33" t="n">
-        <v>0.267</v>
+        <v>-0.008</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="H33" t="n">
-        <v>1.55</v>
+        <v>1.135</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -1788,36 +1788,36 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tom Kim</t>
+          <t>Maverick McNealy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0387</v>
+        <v>0.2071</v>
       </c>
       <c r="C34" t="n">
-        <v>1.9375</v>
+        <v>0.6014</v>
       </c>
       <c r="D34" t="n">
-        <v>1.1887</v>
+        <v>-0.0757</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1275</v>
+        <v>0.6014</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1525</v>
+        <v>0.2971</v>
       </c>
       <c r="G34" t="n">
-        <v>0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="H34" t="n">
-        <v>1.832</v>
+        <v>0.6775</v>
       </c>
       <c r="I34" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -1829,36 +1829,36 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kurt Kitayama</t>
+          <t>Collin Morikawa</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.449</v>
+        <v>0.2425</v>
       </c>
       <c r="C35" t="n">
-        <v>0.185</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>0.581</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>0.026</v>
+        <v>0.765</v>
       </c>
       <c r="F35" t="n">
-        <v>0.031</v>
+        <v>-0.2725</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H35" t="n">
-        <v>1.09</v>
+        <v>1.56</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -1870,36 +1870,36 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jake Knapp</t>
+          <t>Alex Noren</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.337</v>
+        <v>0.2013</v>
       </c>
       <c r="C36" t="n">
-        <v>0.185</v>
+        <v>0.82</v>
       </c>
       <c r="D36" t="n">
-        <v>0.323</v>
+        <v>-0.1787</v>
       </c>
       <c r="E36" t="n">
-        <v>0.225</v>
+        <v>0.6663</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.099</v>
+        <v>0.0775</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="H36" t="n">
-        <v>0.79</v>
+        <v>0.13</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -1911,36 +1911,36 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jackson Koivun</t>
+          <t>J.T. Poston</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.535</v>
+        <v>0.2225</v>
       </c>
       <c r="C37" t="n">
-        <v>0.675</v>
+        <v>0.9712</v>
       </c>
       <c r="D37" t="n">
-        <v>0.37</v>
+        <v>0.1025</v>
       </c>
       <c r="E37" t="n">
-        <v>0.015</v>
+        <v>0.3337</v>
       </c>
       <c r="F37" t="n">
-        <v>0.275</v>
+        <v>0.0013</v>
       </c>
       <c r="G37" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H37" t="n">
-        <v>1.37</v>
+        <v>-0.0425</v>
       </c>
       <c r="I37" t="n">
-        <v>0.02</v>
+        <v>0.14</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -1952,36 +1952,36 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Min Woo Lee</t>
+          <t>Aaron Rai</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.611</v>
+        <v>0.2863</v>
       </c>
       <c r="C38" t="n">
-        <v>0.185</v>
+        <v>0.6887</v>
       </c>
       <c r="D38" t="n">
-        <v>0.395</v>
+        <v>0.5513</v>
       </c>
       <c r="E38" t="n">
-        <v>0.197</v>
+        <v>-0.0163</v>
       </c>
       <c r="F38" t="n">
-        <v>0.218</v>
+        <v>0.1338</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H38" t="n">
-        <v>1.42</v>
+        <v>0.162</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -1993,36 +1993,36 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Shane Lowry</t>
+          <t>Kristoffer Reitan</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.324</v>
+        <v>0.7071</v>
       </c>
       <c r="C39" t="n">
-        <v>0.185</v>
+        <v>0.7729</v>
       </c>
       <c r="D39" t="n">
-        <v>0.708</v>
+        <v>0.2114</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.034</v>
+        <v>0.1914</v>
       </c>
       <c r="F39" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.3086</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="H39" t="n">
-        <v>1.01</v>
+        <v>-0.2275</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2034,36 +2034,36 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Robert MacIntyre</t>
+          <t>Justin Rose</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.391</v>
+        <v>0.1917</v>
       </c>
       <c r="C40" t="n">
-        <v>0.185</v>
+        <v>0.765</v>
       </c>
       <c r="D40" t="n">
-        <v>0.311</v>
+        <v>0.5767</v>
       </c>
       <c r="E40" t="n">
-        <v>0.466</v>
+        <v>0.265</v>
       </c>
       <c r="F40" t="n">
-        <v>0.164</v>
+        <v>-0.09</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="H40" t="n">
-        <v>1.33</v>
+        <v>0.22</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2075,36 +2075,36 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Hideki Matsuyama</t>
+          <t>Xander Schauffele</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.0411</v>
+        <v>0.7143</v>
       </c>
       <c r="C41" t="n">
-        <v>1.07</v>
+        <v>1.4943</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3978</v>
+        <v>0.1157</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1133</v>
+        <v>0.0857</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4278</v>
+        <v>0.1786</v>
       </c>
       <c r="G41" t="n">
-        <v>0.06</v>
+        <v>-0.14</v>
       </c>
       <c r="H41" t="n">
-        <v>1.664</v>
+        <v>1.3225</v>
       </c>
       <c r="I41" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2116,36 +2116,36 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Scottie Scheffler</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.3611</v>
+        <v>0.7429</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2622</v>
+        <v>4.8314</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0078</v>
+        <v>1.22</v>
       </c>
       <c r="E42" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1311</v>
+        <v>0.2243</v>
       </c>
       <c r="G42" t="n">
-        <v>0.09</v>
+        <v>-0.11</v>
       </c>
       <c r="H42" t="n">
-        <v>0.166</v>
+        <v>3.115</v>
       </c>
       <c r="I42" t="n">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2157,36 +2157,36 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Rory McIlroy</t>
+          <t>Adam Scott</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.139</v>
+        <v>0.4</v>
       </c>
       <c r="C43" t="n">
-        <v>0.185</v>
+        <v>0.4983</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="E43" t="n">
-        <v>0.313</v>
+        <v>0.2017</v>
       </c>
       <c r="F43" t="n">
+        <v>-0.2983</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="I43" t="n">
         <v>0.14</v>
       </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2198,36 +2198,36 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Maverick McNealy</t>
+          <t>Alex Smalley</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.1671</v>
+        <v>0.2013</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5343</v>
+        <v>0.8163</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0857</v>
+        <v>0.39</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6129</v>
+        <v>0.39</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3386</v>
+        <v>-0.1</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.13</v>
+        <v>-0.04</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8075</v>
+        <v>0.305</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2239,36 +2239,36 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Keith Mitchell</t>
+          <t>J.J. Spaun</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6456</v>
+        <v>0.3362</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4089</v>
+        <v>0.8712</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3744</v>
+        <v>0.715</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.2989</v>
+        <v>-0.2512</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.0544</v>
+        <v>0.3588</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.746</v>
+        <v>0.4175</v>
       </c>
       <c r="I45" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2280,36 +2280,36 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Collin Morikawa</t>
+          <t>Sepp Straka</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.489</v>
+        <v>-0.1286</v>
       </c>
       <c r="C46" t="n">
-        <v>0.185</v>
+        <v>0.0314</v>
       </c>
       <c r="D46" t="n">
-        <v>0.806</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>0.223</v>
+        <v>-0.6571</v>
       </c>
       <c r="F46" t="n">
-        <v>0.027</v>
+        <v>-0.3</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="H46" t="n">
-        <v>1.54</v>
+        <v>-0.9175</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2321,36 +2321,36 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alex Noren</t>
+          <t>Sahith Theegala</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.2137</v>
+        <v>-0.1356</v>
       </c>
       <c r="C47" t="n">
-        <v>0.82</v>
+        <v>0.0833</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2075</v>
+        <v>0.1144</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7575</v>
+        <v>-0.0389</v>
       </c>
       <c r="F47" t="n">
-        <v>0.08</v>
+        <v>0.1122</v>
       </c>
       <c r="G47" t="n">
-        <v>0.19</v>
+        <v>-0.06</v>
       </c>
       <c r="H47" t="n">
-        <v>0.248</v>
+        <v>0.13</v>
       </c>
       <c r="I47" t="n">
         <v>0.06</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2362,36 +2362,36 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>J.T. Poston</t>
+          <t>Justin Thomas</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.3925</v>
+        <v>0.2562</v>
       </c>
       <c r="C48" t="n">
-        <v>0.91</v>
+        <v>0.8838</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0288</v>
+        <v>0.15</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2537</v>
+        <v>0.2687</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.0775</v>
+        <v>0.7262</v>
       </c>
       <c r="G48" t="n">
-        <v>0.16</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>0.525</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2403,36 +2403,36 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>Michael Thorbjornsen</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4363</v>
+        <v>0.4814</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2275</v>
+        <v>0.6371</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3588</v>
+        <v>-0.0486</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1888</v>
+        <v>-0.2029</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.5029</v>
+        <v>0.2686</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.42</v>
+        <v>-0.1</v>
       </c>
       <c r="H49" t="n">
-        <v>-1.042</v>
+        <v>0.72</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2444,36 +2444,36 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Aaron Rai</t>
+          <t>Gary Woodland</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.3586</v>
+        <v>0.6171</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7871</v>
+        <v>0.6257</v>
       </c>
       <c r="D50" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.0314</v>
       </c>
       <c r="E50" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1557</v>
+        <v>-0.2843</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4</v>
+        <v>-0.08</v>
       </c>
       <c r="H50" t="n">
-        <v>0.724</v>
+        <v>-0.3233</v>
       </c>
       <c r="I50" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -2485,818 +2485,39 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kristoffer Reitan</t>
+          <t>Cameron Young</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.603</v>
+        <v>0.6571</v>
       </c>
       <c r="C51" t="n">
-        <v>0.185</v>
+        <v>0.7271</v>
       </c>
       <c r="D51" t="n">
-        <v>0.239</v>
+        <v>0.6886</v>
       </c>
       <c r="E51" t="n">
-        <v>0.233</v>
+        <v>-0.3914</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.117</v>
+        <v>0.1929</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="H51" t="n">
-        <v>0.96</v>
+        <v>0.855</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>FedEx St. Jude Championship</t>
+          <t>BMW Championship</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Patrick Rodgers</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>-0.2689</v>
-      </c>
-      <c r="C52" t="n">
-        <v>0.0267</v>
-      </c>
-      <c r="D52" t="n">
-        <v>-0.6189</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.1889</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-0.2622</v>
-      </c>
-      <c r="G52" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-1.7225</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>FedEx St. Jude Championship</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Justin Rose</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.517</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>FedEx St. Jude Championship</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Xander Schauffele</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>0.793</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.199</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>FedEx St. Jude Championship</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Scottie Scheffler</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1.096</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>FedEx St. Jude Championship</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Matti Schmid</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>0.1343</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0.1629</v>
-      </c>
-      <c r="D56" t="n">
-        <v>-0.06569999999999999</v>
-      </c>
-      <c r="E56" t="n">
-        <v>-0.4686</v>
-      </c>
-      <c r="F56" t="n">
-        <v>-0.2457</v>
-      </c>
-      <c r="G56" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-0.775</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>FedEx St. Jude Championship</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Adam Scott</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E57" t="n">
-        <v>-0.068</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>FedEx St. Jude Championship</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Alex Smalley</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>0.2562</v>
-      </c>
-      <c r="C58" t="n">
-        <v>1.0263</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0.5038</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.4213</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-0.125</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-0.2975</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>FedEx St. Jude Championship</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Jordan Smith</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>0.4163</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.4625</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0.4913</v>
-      </c>
-      <c r="E59" t="n">
-        <v>-0.0688</v>
-      </c>
-      <c r="F59" t="n">
-        <v>-0.1775</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="H59" t="n">
-        <v>1.1475</v>
-      </c>
-      <c r="I59" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>FedEx St. Jude Championship</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>J.J. Spaun</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0.747</v>
-      </c>
-      <c r="E60" t="n">
-        <v>-0.107</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>FedEx St. Jude Championship</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Jordan Spieth</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0.2711</v>
-      </c>
-      <c r="D61" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="E61" t="n">
-        <v>-0.0267</v>
-      </c>
-      <c r="F61" t="n">
-        <v>-0.0122</v>
-      </c>
-      <c r="G61" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-0.158</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>FedEx St. Jude Championship</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Sam Stevens</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="D62" t="n">
-        <v>-0.008</v>
-      </c>
-      <c r="E62" t="n">
-        <v>-0.514</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="G62" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-0.8817</v>
-      </c>
-      <c r="I62" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>FedEx St. Jude Championship</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Sepp Straka</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>-0.1114</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0.0314</v>
-      </c>
-      <c r="D63" t="n">
-        <v>0.0014</v>
-      </c>
-      <c r="E63" t="n">
-        <v>-0.4357</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-0.915</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>FedEx St. Jude Championship</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Nick Taylor</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>-0.1722</v>
-      </c>
-      <c r="C64" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="D64" t="n">
-        <v>-0.0533</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.7233000000000001</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.0233</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>FedEx St. Jude Championship</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Sahith Theegala</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>-0.0978</v>
-      </c>
-      <c r="C65" t="n">
-        <v>0.1167</v>
-      </c>
-      <c r="D65" t="n">
-        <v>0.2844</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0.2033</v>
-      </c>
-      <c r="G65" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.506</v>
-      </c>
-      <c r="I65" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>FedEx St. Jude Championship</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Justin Thomas</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="C66" t="n">
-        <v>0.9313</v>
-      </c>
-      <c r="D66" t="n">
-        <v>0.3337</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0.2687</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0.6138</v>
-      </c>
-      <c r="G66" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="H66" t="n">
-        <v>1.545</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>FedEx St. Jude Championship</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Michael Thorbjornsen</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>0.549</v>
-      </c>
-      <c r="C67" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="D67" t="n">
-        <v>0.457</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>FedEx St. Jude Championship</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Gary Woodland</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="D68" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F68" t="n">
-        <v>-0.259</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>FedEx St. Jude Championship</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Sudarshan Yellamaraju</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>0.217</v>
-      </c>
-      <c r="C69" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="D69" t="n">
-        <v>-0.001</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>FedEx St. Jude Championship</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Cameron Young</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>0.7929</v>
-      </c>
-      <c r="C70" t="n">
-        <v>2.7529</v>
-      </c>
-      <c r="D70" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E70" t="n">
-        <v>-0.3086</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0.2314</v>
-      </c>
-      <c r="G70" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>FedEx St. Jude Championship</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
         <is>
           <t>PGA Tour</t>
         </is>
